--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,17 +880,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1052,55 +1052,55 @@
         <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1211,55 +1211,55 @@
         <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,55 +1370,55 @@
         <v>3.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AB8" t="n">
         <v>1.51</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,46 +1679,46 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="R8" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
         <v>1.51</v>
@@ -1727,16 +1727,16 @@
         <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,46 +1838,46 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AB9" t="n">
         <v>1.51</v>
@@ -1886,16 +1886,16 @@
         <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU9"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,46 +1679,46 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AB8" t="n">
         <v>1.51</v>
@@ -1727,16 +1727,16 @@
         <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,46 +1838,46 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
         <v>1.51</v>
@@ -1886,16 +1886,16 @@
         <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1942,6 +1942,165 @@
       </c>
       <c r="AU9" s="3" t="n">
         <v>46216.85416666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Colegiales</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>46216.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,46 +1679,46 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="R8" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
         <v>1.51</v>
@@ -1727,16 +1727,16 @@
         <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,46 +1838,46 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AB9" t="n">
         <v>1.51</v>
@@ -1886,16 +1886,16 @@
         <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1361,55 +1361,55 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="R6" t="n">
         <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
         <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA6" t="n">
         <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
@@ -1418,7 +1418,7 @@
         <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
         <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T5" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z5" t="n">
         <v>6.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AF5" t="n">
         <v>1.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
         <v>3.25</v>
@@ -1391,13 +1391,13 @@
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
         <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
         <v>2.05</v>
@@ -1406,10 +1406,10 @@
         <v>1.77</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
         <v>2.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.12</v>
+        <v>2.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T7" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AA7" t="n">
         <v>2.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="O9" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2003,49 +2003,49 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="S10" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="T10" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="U10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="V10" t="n">
         <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.5</v>
+        <v>5.61</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
         <v>1.04</v>
@@ -2070,7 +2070,7 @@
         <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
         <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.22</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S9" t="n">
         <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.33</v>
+        <v>5.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1061,13 +1061,13 @@
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U4" t="n">
         <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
         <v>1.14</v>
@@ -1076,7 +1076,7 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z4" t="n">
         <v>5.5</v>
@@ -1085,19 +1085,19 @@
         <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC4" t="n">
         <v>2.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="n">
         <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
         <v>1.77</v>
@@ -1116,7 +1116,7 @@
         <v>1.13</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q5" t="n">
         <v>2.15</v>
@@ -1220,10 +1220,10 @@
         <v>1.14</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
         <v>1.87</v>
@@ -1235,10 +1235,10 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.55</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.3</v>
@@ -1253,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF5" t="n">
         <v>1.33</v>
@@ -1367,10 +1367,10 @@
         <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
         <v>2.05</v>
@@ -1382,7 +1382,7 @@
         <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
         <v>1.36</v>
@@ -1394,10 +1394,10 @@
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA6" t="n">
         <v>2.05</v>
@@ -1415,7 +1415,7 @@
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AG6" t="n">
         <v>1.91</v>
@@ -1434,7 +1434,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,58 +1520,58 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>2.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.81</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U7" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
         <v>1.94</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
         <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2003,58 +2003,58 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="T10" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="U10" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
         <v>5.61</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S9" t="n">
         <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
         <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="S6" t="n">
         <v>1.4</v>
@@ -1382,31 +1382,31 @@
         <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
         <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
         <v>1.25</v>
@@ -1434,7 +1434,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
         <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.43</v>
+        <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S9" t="n">
         <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,68 +880,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="R6" t="n">
         <v>2.01</v>
@@ -1385,7 +1385,7 @@
         <v>2.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
@@ -1403,7 +1403,7 @@
         <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
         <v>3.5</v>
@@ -1415,7 +1415,7 @@
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
         <v>1.91</v>
@@ -1529,10 +1529,10 @@
         <v>2.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
         <v>1.49</v>
@@ -1541,43 +1541,43 @@
         <v>2.34</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
         <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
         <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
         <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
@@ -1712,13 +1712,13 @@
         <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
         <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
         <v>1.57</v>
@@ -1736,7 +1736,7 @@
         <v>2.03</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="P9" t="n">
         <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="R9" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1049,58 +1049,58 @@
         <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
         <v>2.8</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T4" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
         <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="AA4" t="n">
         <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC4" t="n">
         <v>2.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE4" t="n">
         <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,34 +1202,34 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
         <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="S5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1244,7 +1244,7 @@
         <v>1.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AC5" t="n">
         <v>1.75</v>
@@ -1259,7 +1259,7 @@
         <v>1.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
         <v>2.05</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD8" t="n">
         <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="O9" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD9" t="n">
         <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2009,40 +2009,40 @@
         <v>2.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
         <v>1.67</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
         <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.61</v>
+        <v>6.65</v>
       </c>
       <c r="AD10" t="n">
         <v>1.13</v>
@@ -2054,7 +2054,7 @@
         <v>2.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46216.53125</v>
+        <v>46216.33333333334</v>
       </c>
     </row>
     <row r="3">
@@ -837,7 +837,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -880,7 +880,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46216.58333333334</v>
+        <v>46216.53125</v>
       </c>
     </row>
     <row r="4">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46216.67708333334</v>
+        <v>46216.58333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,81 +1361,81 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.01</v>
+        <v>2.58</v>
       </c>
       <c r="S6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.4</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AF6" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="AG6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK6" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46216.79166666666</v>
+        <v>46216.67708333334</v>
       </c>
     </row>
     <row r="7">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.37</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="V7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.25</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46216.8125</v>
+        <v>46216.79166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T8" t="n">
         <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V8" t="n">
         <v>1.25</v>
       </c>
       <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.04</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46216.85416666666</v>
+        <v>46216.8125</v>
       </c>
     </row>
     <row r="9">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
         <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
         <v>2.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
         <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1950,156 +1950,315 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>46216.85416666666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Argentina Prim B Nacional</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Colegiales</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="N11" t="n">
         <v>1.83</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P11" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" t="n">
         <v>2.45</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.83</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="n">
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3" t="n">
         <v>46216.875</v>
       </c>
     </row>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -746,10 +746,10 @@
         <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -779,10 +779,10 @@
         <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,58 +1838,58 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P9" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="R9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
@@ -1911,7 +1911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,58 +1997,58 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
         <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
         <v>2</v>
@@ -2070,7 +2070,7 @@
         <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -740,10 +740,10 @@
         <v>2.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U2" t="n">
         <v>2.71</v>
@@ -779,10 +779,10 @@
         <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,58 +1838,58 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="R9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
@@ -1911,7 +1911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,58 +1997,58 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P10" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="R10" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="U10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
         <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
         <v>2</v>
@@ -2070,7 +2070,7 @@
         <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
         <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>2.58</v>
       </c>
       <c r="S6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T6" t="n">
         <v>4.6</v>
       </c>
       <c r="U6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.83</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.8</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>6.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AF6" t="n">
         <v>1.33</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1520,28 +1520,28 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="Q7" t="n">
         <v>2.53</v>
       </c>
       <c r="R7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
         <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -1559,7 +1559,7 @@
         <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB7" t="n">
         <v>1.75</v>
@@ -1574,7 +1574,7 @@
         <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
         <v>1.82</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
         <v>1.49</v>
@@ -1700,13 +1700,13 @@
         <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
@@ -1715,28 +1715,28 @@
         <v>1.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC8" t="n">
         <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
         <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,58 +1838,58 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.43</v>
+        <v>2.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
         <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="AD9" t="n">
         <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,58 +1997,58 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.97</v>
+        <v>2.57</v>
       </c>
       <c r="R10" t="n">
         <v>1.91</v>
       </c>
       <c r="S10" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
         <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
         <v>2</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,10 +2189,10 @@
         <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AA11" t="n">
         <v>3.4</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -2177,7 +2177,7 @@
         <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V11" t="n">
         <v>1.14</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
         <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
         <v>2.53</v>
@@ -1544,7 +1544,7 @@
         <v>3.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1553,10 +1553,10 @@
         <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
         <v>2.04</v>
@@ -1568,7 +1568,7 @@
         <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE7" t="n">
         <v>1.07</v>
@@ -2000,10 +2000,10 @@
         <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="Q10" t="n">
         <v>2.57</v>
@@ -2027,7 +2027,7 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
         <v>1.44</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,58 +1838,58 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.88</v>
+        <v>4.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="R9" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
         <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,58 +1997,58 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>4.35</v>
+        <v>2.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
         <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AB10" t="n">
         <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
         <v>2</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -743,7 +743,7 @@
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="U2" t="n">
         <v>2.71</v>
@@ -755,7 +755,7 @@
         <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.25</v>
@@ -767,7 +767,7 @@
         <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
         <v>3.1</v>
@@ -779,10 +779,10 @@
         <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1208,19 +1208,19 @@
         <v>6.15</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R5" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
         <v>2.14</v>
@@ -1232,13 +1232,13 @@
         <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.44</v>
@@ -1253,7 +1253,7 @@
         <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF5" t="n">
         <v>1.94</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK5" t="n">
         <v>3.9</v>
@@ -1361,22 +1361,22 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
         <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="S6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T6" t="n">
         <v>4.6</v>
@@ -1385,7 +1385,7 @@
         <v>1.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W6" t="n">
         <v>1.23</v>
@@ -1400,16 +1400,16 @@
         <v>6.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB6" t="n">
         <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AE6" t="n">
         <v>1.37</v>
@@ -1434,7 +1434,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="Q7" t="n">
         <v>2.53</v>
@@ -1544,7 +1544,7 @@
         <v>3.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1568,7 +1568,7 @@
         <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
         <v>1.07</v>
@@ -1577,7 +1577,7 @@
         <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="P8" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="Q8" t="n">
         <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T8" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
         <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
         <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AK8" t="n">
         <v>1.39</v>
@@ -1841,7 +1841,7 @@
         <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
         <v>4.35</v>
@@ -1868,10 +1868,10 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
         <v>2.54</v>
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="P10" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="R10" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="S10" t="n">
         <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="U10" t="n">
         <v>3.25</v>
@@ -2027,28 +2027,28 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
         <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
         <v>2</v>
@@ -2070,7 +2070,7 @@
         <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
         <v>2.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
         <v>1.57</v>
@@ -2198,13 +2198,13 @@
         <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -743,13 +743,13 @@
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -758,16 +758,16 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC2" t="n">
         <v>3.1</v>
@@ -776,13 +776,13 @@
         <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,58 +1838,58 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.57</v>
+        <v>2.83</v>
       </c>
       <c r="R9" t="n">
         <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,58 +1997,58 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>4.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="R10" t="n">
         <v>1.91</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AB10" t="n">
         <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
         <v>2</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -743,16 +743,16 @@
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -767,7 +767,7 @@
         <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC2" t="n">
         <v>3.1</v>
@@ -779,10 +779,10 @@
         <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1205,16 +1205,16 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="S5" t="n">
         <v>1.23</v>
@@ -1223,19 +1223,19 @@
         <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
         <v>5.5</v>
@@ -1244,19 +1244,19 @@
         <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
         <v>1.83</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
         <v>3.9</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R2" t="n">
         <v>2.2</v>
@@ -743,19 +743,19 @@
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
         <v>1.26</v>
@@ -767,7 +767,7 @@
         <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC2" t="n">
         <v>3.1</v>
@@ -779,10 +779,10 @@
         <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="P5" t="n">
         <v>8.9</v>
@@ -1220,13 +1220,13 @@
         <v>1.23</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
         <v>2.13</v>
       </c>
       <c r="V5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
         <v>1.17</v>
@@ -1235,10 +1235,10 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA5" t="n">
         <v>1.44</v>
@@ -1250,16 +1250,16 @@
         <v>1.96</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
         <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,28 +1520,28 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.53</v>
+        <v>3.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="R7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -1565,19 +1565,19 @@
         <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD7" t="n">
         <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="P8" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.89</v>
@@ -1709,13 +1709,13 @@
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
         <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AA8" t="n">
         <v>2.45</v>
@@ -1733,10 +1733,10 @@
         <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
         <v>1.39</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,58 +1838,58 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4</v>
+        <v>4.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="R9" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
         <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P10" t="n">
-        <v>4.35</v>
+        <v>3.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>2.83</v>
       </c>
       <c r="R10" t="n">
         <v>1.91</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
         <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -2171,10 +2171,10 @@
         <v>1.85</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="T11" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
         <v>4.33</v>
@@ -2198,7 +2198,7 @@
         <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
         <v>7</v>
@@ -2207,7 +2207,7 @@
         <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
         <v>2.5</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1361,55 +1361,55 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
         <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>2.75</v>
       </c>
       <c r="S6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T6" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB6" t="n">
         <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>1.37</v>
@@ -1434,7 +1434,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
         <v>3.94</v>
@@ -1550,13 +1550,13 @@
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
         <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
         <v>2.04</v>
@@ -1574,10 +1574,10 @@
         <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
         <v>2.99</v>
@@ -1691,7 +1691,7 @@
         <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
         <v>1.47</v>
@@ -1721,7 +1721,7 @@
         <v>2.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
         <v>4.25</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,13 +1847,13 @@
         <v>4.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
         <v>2.55</v>
@@ -1865,10 +1865,10 @@
         <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
         <v>1.4</v>
@@ -1877,16 +1877,16 @@
         <v>2.54</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.06</v>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="O10" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
         <v>3.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="R10" t="n">
         <v>1.91</v>
@@ -2015,7 +2015,7 @@
         <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
         <v>3.25</v>
@@ -2024,13 +2024,13 @@
         <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
         <v>2.63</v>
@@ -2045,7 +2045,7 @@
         <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
         <v>1.03</v>
@@ -2171,34 +2171,34 @@
         <v>1.85</v>
       </c>
       <c r="S11" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
         <v>7</v>
@@ -2207,13 +2207,13 @@
         <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
         <v>2.49</v>
@@ -1541,7 +1541,7 @@
         <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -1550,13 +1550,13 @@
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
         <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
         <v>2.04</v>
@@ -1574,10 +1574,10 @@
         <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>4.35</v>
+        <v>3.27</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="R9" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
         <v>1.28</v>
@@ -1868,34 +1868,34 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.27</v>
+        <v>4.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T10" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="U10" t="n">
         <v>3.25</v>
@@ -2027,34 +2027,34 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
         <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1679,49 +1679,49 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="P8" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T8" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
         <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC8" t="n">
         <v>4.25</v>
@@ -1730,13 +1730,13 @@
         <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
         <v>1.94</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
         <v>3.27</v>
@@ -1895,7 +1895,7 @@
         <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R2" t="n">
         <v>2.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
         <v>1.26</v>
@@ -764,25 +764,25 @@
         <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
         <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,34 +1361,34 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="P6" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="S6" t="n">
         <v>1.15</v>
       </c>
       <c r="T6" t="n">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
         <v>1.85</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1403,13 +1403,13 @@
         <v>1.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AE6" t="n">
         <v>1.37</v>
@@ -1434,7 +1434,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,49 +1520,49 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="R7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
         <v>3.6</v>
@@ -1574,10 +1574,10 @@
         <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1682,19 +1682,19 @@
         <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="P8" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
         <v>1.89</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T8" t="n">
         <v>2.36</v>
@@ -1703,28 +1703,28 @@
         <v>3.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
         <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AA8" t="n">
         <v>2.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
         <v>1.17</v>
@@ -1733,10 +1733,10 @@
         <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>3.27</v>
+        <v>3.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S9" t="n">
         <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
         <v>3.25</v>
@@ -1877,7 +1877,7 @@
         <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
         <v>1.52</v>
@@ -1886,16 +1886,16 @@
         <v>4.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
         <v>2.6</v>
@@ -2015,7 +2015,7 @@
         <v>1.51</v>
       </c>
       <c r="T10" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
         <v>3.25</v>
@@ -2033,13 +2033,13 @@
         <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="AA10" t="n">
         <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
         <v>4.33</v>
@@ -2051,7 +2051,7 @@
         <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
         <v>1.73</v>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
         <v>1.85</v>
@@ -2156,55 +2156,55 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
         <v>1.85</v>
       </c>
       <c r="S11" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
         <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AA11" t="n">
         <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R2" t="n">
         <v>2.2</v>
@@ -755,7 +755,7 @@
         <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
         <v>1.26</v>
@@ -773,16 +773,16 @@
         <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
         <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1841,22 +1841,22 @@
         <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.87</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
         <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
         <v>3.25</v>
@@ -1868,34 +1868,34 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2000,22 +2000,22 @@
         <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>3.87</v>
       </c>
       <c r="Q10" t="n">
         <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S10" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
         <v>3.25</v>
@@ -2027,34 +2027,34 @@
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46216.33333333334</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P4" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T4" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.9</v>
+        <v>6.37</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC4" t="n">
         <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.61</v>
+        <v>3.9</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1039,68 +1039,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.37</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4.2</v>
+        <v>4.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="R6" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T6" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="AA6" t="n">
         <v>1.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AF6" t="n">
         <v>1.33</v>
       </c>
       <c r="AG6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1523,58 +1523,58 @@
         <v>1.97</v>
       </c>
       <c r="O7" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T7" t="n">
         <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
         <v>3.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
         <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
         <v>1.91</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="O8" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.91</v>
+        <v>3.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AA8" t="n">
         <v>2.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
         <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="Q9" t="n">
         <v>2.6</v>
@@ -1853,31 +1853,31 @@
         <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="U9" t="n">
         <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
@@ -1889,13 +1889,13 @@
         <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" t="n">
         <v>2.6</v>
@@ -2015,7 +2015,7 @@
         <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
         <v>3.25</v>
@@ -2024,7 +2024,7 @@
         <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
@@ -2036,16 +2036,16 @@
         <v>2.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AB10" t="n">
         <v>1.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
         <v>1.01</v>
@@ -2054,7 +2054,7 @@
         <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="P11" t="n">
-        <v>4.85</v>
+        <v>3.85</v>
       </c>
       <c r="Q11" t="n">
         <v>2.5</v>
@@ -2174,43 +2174,43 @@
         <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
         <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Y11" t="n">
         <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AG11" t="n">
         <v>1.53</v>

--- a/jogos_2026-07-13.xlsx
+++ b/jogos_2026-07-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,139 +1011,139 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>['28', '45', '57']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46216.58333333334</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,68 +1198,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>4.98</v>
+        <v>3.72</v>
       </c>
       <c r="Q6" t="n">
         <v>1.93</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S6" t="n">
         <v>1.13</v>
@@ -1382,13 +1382,13 @@
         <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V6" t="n">
         <v>1.95</v>
       </c>
       <c r="W6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1397,13 +1397,13 @@
         <v>1.03</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA6" t="n">
         <v>1.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC6" t="n">
         <v>1.75</v>
@@ -1412,10 +1412,10 @@
         <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AG6" t="n">
         <v>2.6</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
         <v>3.9</v>
@@ -1574,7 +1574,7 @@
         <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG7" t="n">
         <v>1.91</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="O8" t="n">
         <v>2.8</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
         <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>4.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
         <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
         <v>1.66</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,61 +1997,61 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="n">
         <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T10" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="U10" t="n">
         <v>3.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
         <v>1.66</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.85</v>
+        <v>5.35</v>
       </c>
       <c r="Q11" t="n">
         <v>2.5</v>
@@ -2198,7 +2198,7 @@
         <v>2.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
         <v>7</v>
